--- a/data/SEMANA ATUAL/LIMPEZA PERFUMARIA.xlsx
+++ b/data/SEMANA ATUAL/LIMPEZA PERFUMARIA.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="274">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="277">
   <si>
     <t>Sigla Loja</t>
   </si>
@@ -28,6 +28,9 @@
     <t>21/07/2026 (Ter)</t>
   </si>
   <si>
+    <t>22/07/2026 (Qua)</t>
+  </si>
+  <si>
     <t>ABNO-RJ</t>
   </si>
   <si>
@@ -836,6 +839,12 @@
   </si>
   <si>
     <t>ZBND-MG</t>
+  </si>
+  <si>
+    <t>ZTMP-SP</t>
+  </si>
+  <si>
+    <t>ZVJD-SP</t>
   </si>
 </sst>
 </file>
@@ -1201,7 +1210,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D270"/>
+  <dimension ref="A1:E272"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1209,7 +1218,7 @@
     <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:5">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1222,10 +1231,13 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C2" s="1">
         <v>221.15</v>
@@ -1233,10 +1245,13 @@
       <c r="D2" s="1">
         <v>67.78</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
+      <c r="E2" s="1">
+        <v>176.14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
       <c r="A3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
         <v>603.7199999999999</v>
@@ -1244,21 +1259,27 @@
       <c r="D3" s="1">
         <v>450.8800000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
+      <c r="E3" s="1">
+        <v>392.11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1">
-        <v>500.0500000000001</v>
+        <v>500.05</v>
       </c>
       <c r="D4" s="1">
         <v>468.6100000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
+      <c r="E4" s="1">
+        <v>719.6500000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1">
         <v>514.54</v>
@@ -1266,10 +1287,13 @@
       <c r="D5" s="1">
         <v>122.16</v>
       </c>
-    </row>
-    <row r="6" spans="1:4">
+      <c r="E5" s="1">
+        <v>356.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>467.77</v>
@@ -1277,21 +1301,27 @@
       <c r="D6" s="1">
         <v>225.33</v>
       </c>
-    </row>
-    <row r="7" spans="1:4">
+      <c r="E6" s="1">
+        <v>324.0500000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>622.59</v>
       </c>
       <c r="D7" s="1">
-        <v>454.5700000000001</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
+        <v>454.57</v>
+      </c>
+      <c r="E7" s="1">
+        <v>520.75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>244.42</v>
@@ -1299,10 +1329,13 @@
       <c r="D8" s="1">
         <v>225.15</v>
       </c>
-    </row>
-    <row r="9" spans="1:4">
+      <c r="E8" s="1">
+        <v>164.75</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>533.96</v>
@@ -1310,10 +1343,13 @@
       <c r="D9" s="1">
         <v>202.93</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
+      <c r="E9" s="1">
+        <v>270.95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>106.25</v>
@@ -1321,10 +1357,13 @@
       <c r="D10" s="1">
         <v>185.86</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
+      <c r="E10" s="1">
+        <v>132.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
       <c r="A11" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" s="1">
         <v>381.46</v>
@@ -1332,10 +1371,13 @@
       <c r="D11" s="1">
         <v>250.13</v>
       </c>
-    </row>
-    <row r="12" spans="1:4">
+      <c r="E11" s="1">
+        <v>476.8100000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
       <c r="A12" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" s="1">
         <v>78.77000000000001</v>
@@ -1343,21 +1385,27 @@
       <c r="D12" s="1">
         <v>91.95999999999999</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
+      <c r="E12" s="1">
+        <v>139.97</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" s="1">
-        <v>517.5699999999999</v>
+        <v>517.5700000000001</v>
       </c>
       <c r="D13" s="1">
         <v>483.26</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
+      <c r="E13" s="1">
+        <v>296.6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
       <c r="A14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" s="1">
         <v>498.7</v>
@@ -1365,10 +1413,13 @@
       <c r="D14" s="1">
         <v>230.74</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
+      <c r="E14" s="1">
+        <v>304.92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" s="1">
         <v>319.89</v>
@@ -1376,10 +1427,13 @@
       <c r="D15" s="1">
         <v>236.76</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
+      <c r="E15" s="1">
+        <v>286.97</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
       <c r="A16" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" s="1">
         <v>122.96</v>
@@ -1387,10 +1441,13 @@
       <c r="D16" s="1">
         <v>159.14</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" s="1">
+        <v>88.45999999999999</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" s="1">
         <v>227.7</v>
@@ -1398,10 +1455,13 @@
       <c r="D17" s="1">
         <v>487.45</v>
       </c>
-    </row>
-    <row r="18" spans="1:4">
+      <c r="E17" s="1">
+        <v>207.96</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
       <c r="A18" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" s="1">
         <v>81.98</v>
@@ -1409,21 +1469,27 @@
       <c r="D18" s="1">
         <v>134.23</v>
       </c>
-    </row>
-    <row r="19" spans="1:4">
+      <c r="E18" s="1">
+        <v>287.5700000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" s="1">
-        <v>450.57</v>
+        <v>450.5700000000001</v>
       </c>
       <c r="D19" s="1">
         <v>437.28</v>
       </c>
-    </row>
-    <row r="20" spans="1:4">
+      <c r="E19" s="1">
+        <v>611.22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C20" s="1">
         <v>184.9</v>
@@ -1431,10 +1497,13 @@
       <c r="D20" s="1">
         <v>353.71</v>
       </c>
-    </row>
-    <row r="21" spans="1:4">
+      <c r="E20" s="1">
+        <v>285.08</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
       <c r="A21" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1">
         <v>49.98</v>
@@ -1442,10 +1511,13 @@
       <c r="D21" s="1">
         <v>23.98</v>
       </c>
-    </row>
-    <row r="22" spans="1:4">
+      <c r="E21" s="1">
+        <v>96.53999999999999</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
       <c r="A22" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C22" s="1">
         <v>100.97</v>
@@ -1453,10 +1525,13 @@
       <c r="D22" s="1">
         <v>135.8</v>
       </c>
-    </row>
-    <row r="23" spans="1:4">
+      <c r="E22" s="1">
+        <v>141.15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C23" s="1">
         <v>15.49</v>
@@ -1464,10 +1539,13 @@
       <c r="D23" s="1">
         <v>26.99</v>
       </c>
-    </row>
-    <row r="24" spans="1:4">
+      <c r="E23" s="1">
+        <v>145.55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" s="1">
         <v>178.15</v>
@@ -1475,10 +1553,13 @@
       <c r="D24" s="1">
         <v>206.48</v>
       </c>
-    </row>
-    <row r="25" spans="1:4">
+      <c r="E24" s="1">
+        <v>121.66</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
       <c r="A25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C25" s="1">
         <v>65.56999999999999</v>
@@ -1486,21 +1567,27 @@
       <c r="D25" s="1">
         <v>83.97</v>
       </c>
-    </row>
-    <row r="26" spans="1:4">
+      <c r="E25" s="1">
+        <v>40.48</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
       <c r="A26" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C26" s="1">
         <v>552.0700000000001</v>
       </c>
       <c r="D26" s="1">
-        <v>973.62</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
+        <v>973.6200000000001</v>
+      </c>
+      <c r="E26" s="1">
+        <v>776.22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
       <c r="A27" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1">
         <v>83.72</v>
@@ -1508,32 +1595,41 @@
       <c r="D27" s="1">
         <v>369.53</v>
       </c>
-    </row>
-    <row r="28" spans="1:4">
+      <c r="E27" s="1">
+        <v>66.19</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
       <c r="A28" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C28" s="1">
-        <v>908.6400000000001</v>
+        <v>908.64</v>
       </c>
       <c r="D28" s="1">
         <v>708.9100000000001</v>
       </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="E28" s="1">
+        <v>484.47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="1">
-        <v>954.8000000000002</v>
+        <v>954.8</v>
       </c>
       <c r="D29" s="1">
         <v>822.3000000000002</v>
       </c>
-    </row>
-    <row r="30" spans="1:4">
+      <c r="E29" s="1">
+        <v>1047.82</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
       <c r="A30" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="1">
         <v>309.71</v>
@@ -1541,10 +1637,13 @@
       <c r="D30" s="1">
         <v>212.85</v>
       </c>
-    </row>
-    <row r="31" spans="1:4">
+      <c r="E30" s="1">
+        <v>78.17999999999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
       <c r="A31" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C31" s="1">
         <v>108.96</v>
@@ -1552,43 +1651,55 @@
       <c r="D31" s="1">
         <v>106.76</v>
       </c>
-    </row>
-    <row r="32" spans="1:4">
+      <c r="E31" s="1">
+        <v>278.67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
       <c r="A32" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C32" s="1">
-        <v>350.8600000000001</v>
+        <v>350.86</v>
       </c>
       <c r="D32" s="1">
         <v>546.15</v>
       </c>
-    </row>
-    <row r="33" spans="1:4">
+      <c r="E32" s="1">
+        <v>482.21</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
       <c r="A33" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C33" s="1">
-        <v>740.2100000000002</v>
+        <v>740.2099999999999</v>
       </c>
       <c r="D33" s="1">
         <v>325.58</v>
       </c>
-    </row>
-    <row r="34" spans="1:4">
+      <c r="E33" s="1">
+        <v>594.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
       <c r="A34" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C34" s="1">
         <v>740.5</v>
       </c>
       <c r="D34" s="1">
-        <v>946.34</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
+        <v>965.33</v>
+      </c>
+      <c r="E34" s="1">
+        <v>702.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
       <c r="A35" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C35" s="1">
         <v>251.41</v>
@@ -1596,10 +1707,13 @@
       <c r="D35" s="1">
         <v>62.47</v>
       </c>
-    </row>
-    <row r="36" spans="1:4">
+      <c r="E35" s="1">
+        <v>84.97</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
       <c r="A36" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C36" s="1">
         <v>382.23</v>
@@ -1607,10 +1721,13 @@
       <c r="D36" s="1">
         <v>581.6000000000001</v>
       </c>
-    </row>
-    <row r="37" spans="1:4">
+      <c r="E36" s="1">
+        <v>517.5799999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
       <c r="A37" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C37" s="1">
         <v>855.7600000000001</v>
@@ -1618,10 +1735,13 @@
       <c r="D37" s="1">
         <v>545.39</v>
       </c>
-    </row>
-    <row r="38" spans="1:4">
+      <c r="E37" s="1">
+        <v>799.89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
       <c r="A38" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C38" s="1">
         <v>69.98</v>
@@ -1629,32 +1749,41 @@
       <c r="D38" s="1">
         <v>149.92</v>
       </c>
-    </row>
-    <row r="39" spans="1:4">
+      <c r="E38" s="1">
+        <v>119.48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
       <c r="A39" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D39" s="1">
         <v>104.45</v>
       </c>
-    </row>
-    <row r="40" spans="1:4">
+      <c r="E39" s="1">
+        <v>173.54</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
       <c r="A40" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C40" s="1">
-        <v>372.3099999999999</v>
+        <v>372.3100000000001</v>
       </c>
       <c r="D40" s="1">
         <v>380.59</v>
       </c>
-    </row>
-    <row r="41" spans="1:4">
+      <c r="E40" s="1">
+        <v>222.08</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
       <c r="A41" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C41" s="1">
         <v>266.3</v>
@@ -1662,10 +1791,13 @@
       <c r="D41" s="1">
         <v>273.04</v>
       </c>
-    </row>
-    <row r="42" spans="1:4">
+      <c r="E41" s="1">
+        <v>227.68</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
       <c r="A42" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C42" s="1">
         <v>332.98</v>
@@ -1673,10 +1805,13 @@
       <c r="D42" s="1">
         <v>198.36</v>
       </c>
-    </row>
-    <row r="43" spans="1:4">
+      <c r="E42" s="1">
+        <v>279.8</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
       <c r="A43" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C43" s="1">
         <v>102.47</v>
@@ -1684,10 +1819,13 @@
       <c r="D43" s="1">
         <v>119.86</v>
       </c>
-    </row>
-    <row r="44" spans="1:4">
+      <c r="E43" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
       <c r="A44" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C44" s="1">
         <v>333.21</v>
@@ -1695,32 +1833,41 @@
       <c r="D44" s="1">
         <v>351.7</v>
       </c>
-    </row>
-    <row r="45" spans="1:4">
+      <c r="E44" s="1">
+        <v>318.8800000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
       <c r="A45" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C45" s="1">
-        <v>515.9000000000001</v>
+        <v>515.9</v>
       </c>
       <c r="D45" s="1">
-        <v>643.55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
+        <v>643.5500000000002</v>
+      </c>
+      <c r="E45" s="1">
+        <v>414.11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
       <c r="A46" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C46" s="1">
-        <v>550.4399999999999</v>
+        <v>550.4400000000001</v>
       </c>
       <c r="D46" s="1">
         <v>600.39</v>
       </c>
-    </row>
-    <row r="47" spans="1:4">
+      <c r="E46" s="1">
+        <v>651.1799999999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
       <c r="A47" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C47" s="1">
         <v>209.92</v>
@@ -1728,32 +1875,41 @@
       <c r="D47" s="1">
         <v>186.72</v>
       </c>
-    </row>
-    <row r="48" spans="1:4">
+      <c r="E47" s="1">
+        <v>160.04</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
       <c r="A48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C48" s="1">
-        <v>413.86</v>
+        <v>413.8600000000001</v>
       </c>
       <c r="D48" s="1">
         <v>339.14</v>
       </c>
-    </row>
-    <row r="49" spans="1:4">
+      <c r="E48" s="1">
+        <v>746.6200000000001</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
       <c r="A49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C49" s="1">
-        <v>590.5399999999998</v>
+        <v>590.54</v>
       </c>
       <c r="D49" s="1">
-        <v>574.1399999999999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
+        <v>574.14</v>
+      </c>
+      <c r="E49" s="1">
+        <v>795.3400000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
       <c r="A50" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C50" s="1">
         <v>18.99</v>
@@ -1761,10 +1917,13 @@
       <c r="D50" s="1">
         <v>46.97</v>
       </c>
-    </row>
-    <row r="51" spans="1:4">
+      <c r="E50" s="1">
+        <v>69.06999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
       <c r="A51" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C51" s="1">
         <v>147.07</v>
@@ -1772,10 +1931,13 @@
       <c r="D51" s="1">
         <v>117.96</v>
       </c>
-    </row>
-    <row r="52" spans="1:4">
+      <c r="E51" s="1">
+        <v>209.75</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
       <c r="A52" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C52" s="1">
         <v>216.55</v>
@@ -1783,10 +1945,13 @@
       <c r="D52" s="1">
         <v>150.08</v>
       </c>
-    </row>
-    <row r="53" spans="1:4">
+      <c r="E52" s="1">
+        <v>87.91999999999999</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
       <c r="A53" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C53" s="1">
         <v>180.97</v>
@@ -1794,10 +1959,13 @@
       <c r="D53" s="1">
         <v>131.78</v>
       </c>
-    </row>
-    <row r="54" spans="1:4">
+      <c r="E53" s="1">
+        <v>64.78</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
       <c r="A54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C54" s="1">
         <v>66.98</v>
@@ -1805,10 +1973,13 @@
       <c r="D54" s="1">
         <v>33.98</v>
       </c>
-    </row>
-    <row r="55" spans="1:4">
+      <c r="E54" s="1">
+        <v>19.8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
       <c r="A55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C55" s="1">
         <v>162.38</v>
@@ -1816,10 +1987,13 @@
       <c r="D55" s="1">
         <v>66.09</v>
       </c>
-    </row>
-    <row r="56" spans="1:4">
+      <c r="E55" s="1">
+        <v>181.24</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
       <c r="A56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C56" s="1">
         <v>192.75</v>
@@ -1827,10 +2001,13 @@
       <c r="D56" s="1">
         <v>150.93</v>
       </c>
-    </row>
-    <row r="57" spans="1:4">
+      <c r="E56" s="1">
+        <v>40.98</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
       <c r="A57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C57" s="1">
         <v>696.5599999999999</v>
@@ -1838,10 +2015,13 @@
       <c r="D57" s="1">
         <v>988.92</v>
       </c>
-    </row>
-    <row r="58" spans="1:4">
+      <c r="E57" s="1">
+        <v>1378.41</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
       <c r="A58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C58" s="1">
         <v>395.29</v>
@@ -1849,10 +2029,13 @@
       <c r="D58" s="1">
         <v>164.16</v>
       </c>
-    </row>
-    <row r="59" spans="1:4">
+      <c r="E58" s="1">
+        <v>441.54</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
       <c r="A59" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C59" s="1">
         <v>427.3</v>
@@ -1860,21 +2043,27 @@
       <c r="D59" s="1">
         <v>236.51</v>
       </c>
-    </row>
-    <row r="60" spans="1:4">
+      <c r="E59" s="1">
+        <v>147.71</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
       <c r="A60" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D60" s="1">
         <v>49.99000000000001</v>
       </c>
-    </row>
-    <row r="61" spans="1:4">
+      <c r="E60" s="1">
+        <v>39.99</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
       <c r="A61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C61" s="1">
         <v>126.16</v>
@@ -1882,10 +2071,13 @@
       <c r="D61" s="1">
         <v>246.41</v>
       </c>
-    </row>
-    <row r="62" spans="1:4">
+      <c r="E61" s="1">
+        <v>66.48</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
       <c r="A62" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C62" s="1">
         <v>372.75</v>
@@ -1893,10 +2085,13 @@
       <c r="D62" s="1">
         <v>463.77</v>
       </c>
-    </row>
-    <row r="63" spans="1:4">
+      <c r="E62" s="1">
+        <v>428.27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
       <c r="A63" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C63" s="1">
         <v>19.8</v>
@@ -1904,21 +2099,27 @@
       <c r="D63" s="1">
         <v>116.46</v>
       </c>
-    </row>
-    <row r="64" spans="1:4">
+      <c r="E63" s="1">
+        <v>-14</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5">
       <c r="A64" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C64" s="1">
         <v>234.32</v>
       </c>
       <c r="D64" s="1">
-        <v>941.4900000000001</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
+        <v>941.49</v>
+      </c>
+      <c r="E64" s="1">
+        <v>221.44</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
       <c r="A65" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C65" s="1">
         <v>100.17</v>
@@ -1926,10 +2127,13 @@
       <c r="D65" s="1">
         <v>254.28</v>
       </c>
-    </row>
-    <row r="66" spans="1:4">
+      <c r="E65" s="1">
+        <v>143.34</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
       <c r="A66" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C66" s="1">
         <v>82.97</v>
@@ -1937,10 +2141,13 @@
       <c r="D66" s="1">
         <v>107.47</v>
       </c>
-    </row>
-    <row r="67" spans="1:4">
+      <c r="E66" s="1">
+        <v>145.64</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
       <c r="A67" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C67" s="1">
         <v>299.23</v>
@@ -1948,10 +2155,13 @@
       <c r="D67" s="1">
         <v>151.84</v>
       </c>
-    </row>
-    <row r="68" spans="1:4">
+      <c r="E67" s="1">
+        <v>284.34</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
       <c r="A68" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C68" s="1">
         <v>138.94</v>
@@ -1959,21 +2169,27 @@
       <c r="D68" s="1">
         <v>125.96</v>
       </c>
-    </row>
-    <row r="69" spans="1:4">
+      <c r="E68" s="1">
+        <v>23.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
       <c r="A69" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C69" s="1">
         <v>60.4</v>
       </c>
       <c r="D69" s="1">
-        <v>134.26</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
+        <v>150.25</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
       <c r="A70" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C70" s="1">
         <v>140.35</v>
@@ -1981,21 +2197,27 @@
       <c r="D70" s="1">
         <v>149.93</v>
       </c>
-    </row>
-    <row r="71" spans="1:4">
+      <c r="E70" s="1">
+        <v>85.75999999999999</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
       <c r="A71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C71" s="1">
-        <v>508.3100000000001</v>
+        <v>508.3099999999999</v>
       </c>
       <c r="D71" s="1">
         <v>230.98</v>
       </c>
-    </row>
-    <row r="72" spans="1:4">
+      <c r="E71" s="1">
+        <v>489.09</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5">
       <c r="A72" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C72" s="1">
         <v>153.76</v>
@@ -2003,10 +2225,13 @@
       <c r="D72" s="1">
         <v>221.86</v>
       </c>
-    </row>
-    <row r="73" spans="1:4">
+      <c r="E72" s="1">
+        <v>141.74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
       <c r="A73" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C73" s="1">
         <v>226.01</v>
@@ -2014,10 +2239,13 @@
       <c r="D73" s="1">
         <v>179.73</v>
       </c>
-    </row>
-    <row r="74" spans="1:4">
+      <c r="E73" s="1">
+        <v>571.0500000000001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5">
       <c r="A74" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C74" s="1">
         <v>489.1100000000001</v>
@@ -2025,10 +2253,13 @@
       <c r="D74" s="1">
         <v>339.6900000000001</v>
       </c>
-    </row>
-    <row r="75" spans="1:4">
+      <c r="E74" s="1">
+        <v>232.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5">
       <c r="A75" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C75" s="1">
         <v>193.05</v>
@@ -2036,10 +2267,13 @@
       <c r="D75" s="1">
         <v>153.74</v>
       </c>
-    </row>
-    <row r="76" spans="1:4">
+      <c r="E75" s="1">
+        <v>213.64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5">
       <c r="A76" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C76" s="1">
         <v>123.57</v>
@@ -2047,10 +2281,13 @@
       <c r="D76" s="1">
         <v>213.71</v>
       </c>
-    </row>
-    <row r="77" spans="1:4">
+      <c r="E76" s="1">
+        <v>350.39</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5">
       <c r="A77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C77" s="1">
         <v>264.98</v>
@@ -2058,10 +2295,13 @@
       <c r="D77" s="1">
         <v>42.99</v>
       </c>
-    </row>
-    <row r="78" spans="1:4">
+      <c r="E77" s="1">
+        <v>308.52</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5">
       <c r="A78" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C78" s="1">
         <v>187.73</v>
@@ -2069,10 +2309,13 @@
       <c r="D78" s="1">
         <v>205.38</v>
       </c>
-    </row>
-    <row r="79" spans="1:4">
+      <c r="E78" s="1">
+        <v>324.96</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5">
       <c r="A79" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C79" s="1">
         <v>104.67</v>
@@ -2080,10 +2323,13 @@
       <c r="D79" s="1">
         <v>97.41999999999999</v>
       </c>
-    </row>
-    <row r="80" spans="1:4">
+      <c r="E79" s="1">
+        <v>171.93</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5">
       <c r="A80" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C80" s="1">
         <v>194.77</v>
@@ -2091,21 +2337,27 @@
       <c r="D80" s="1">
         <v>201.36</v>
       </c>
-    </row>
-    <row r="81" spans="1:4">
+      <c r="E80" s="1">
+        <v>175.98</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5">
       <c r="A81" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C81" s="1">
-        <v>511.2800000000001</v>
+        <v>511.28</v>
       </c>
       <c r="D81" s="1">
         <v>50.19</v>
       </c>
-    </row>
-    <row r="82" spans="1:4">
+      <c r="E81" s="1">
+        <v>303.1</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5">
       <c r="A82" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C82" s="1">
         <v>174.88</v>
@@ -2113,10 +2365,13 @@
       <c r="D82" s="1">
         <v>234.21</v>
       </c>
-    </row>
-    <row r="83" spans="1:4">
+      <c r="E82" s="1">
+        <v>328.11</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5">
       <c r="A83" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C83" s="1">
         <v>155.74</v>
@@ -2124,21 +2379,27 @@
       <c r="D83" s="1">
         <v>103.01</v>
       </c>
-    </row>
-    <row r="84" spans="1:4">
+      <c r="E83" s="1">
+        <v>45.98</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5">
       <c r="A84" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C84" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D84" s="1">
         <v>112.96</v>
       </c>
-    </row>
-    <row r="85" spans="1:4">
+      <c r="E84" s="1">
+        <v>125.05</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5">
       <c r="A85" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C85" s="1">
         <v>110.68</v>
@@ -2146,21 +2407,27 @@
       <c r="D85" s="1">
         <v>160.76</v>
       </c>
-    </row>
-    <row r="86" spans="1:4">
+      <c r="E85" s="1">
+        <v>218.95</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5">
       <c r="A86" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C86" s="1">
-        <v>959.41</v>
+        <v>959.4100000000001</v>
       </c>
       <c r="D86" s="1">
         <v>865.78</v>
       </c>
-    </row>
-    <row r="87" spans="1:4">
+      <c r="E86" s="1">
+        <v>995.9800000000001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5">
       <c r="A87" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C87" s="1">
         <v>132.95</v>
@@ -2168,10 +2435,13 @@
       <c r="D87" s="1">
         <v>111.96</v>
       </c>
-    </row>
-    <row r="88" spans="1:4">
+      <c r="E87" s="1">
+        <v>204.01</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5">
       <c r="A88" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C88" s="1">
         <v>159.94</v>
@@ -2179,10 +2449,13 @@
       <c r="D88" s="1">
         <v>47.98</v>
       </c>
-    </row>
-    <row r="89" spans="1:4">
+      <c r="E88" s="1">
+        <v>57.79</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5">
       <c r="A89" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C89" s="1">
         <v>146.59</v>
@@ -2190,10 +2463,13 @@
       <c r="D89" s="1">
         <v>32.98</v>
       </c>
-    </row>
-    <row r="90" spans="1:4">
+      <c r="E89" s="1">
+        <v>84.06</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5">
       <c r="A90" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C90" s="1">
         <v>250.54</v>
@@ -2201,32 +2477,41 @@
       <c r="D90" s="1">
         <v>145.76</v>
       </c>
-    </row>
-    <row r="91" spans="1:4">
+      <c r="E90" s="1">
+        <v>274.6200000000001</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5">
       <c r="A91" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C91" s="1">
-        <v>403.7199999999999</v>
+        <v>403.72</v>
       </c>
       <c r="D91" s="1">
         <v>233.35</v>
       </c>
-    </row>
-    <row r="92" spans="1:4">
+      <c r="E91" s="1">
+        <v>278.35</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5">
       <c r="A92" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C92" s="1">
         <v>234.44</v>
       </c>
       <c r="D92" s="1">
-        <v>252.93</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
+        <v>252.9300000000001</v>
+      </c>
+      <c r="E92" s="1">
+        <v>342.6300000000001</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5">
       <c r="A93" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C93" s="1">
         <v>495.96</v>
@@ -2234,10 +2519,13 @@
       <c r="D93" s="1">
         <v>342.45</v>
       </c>
-    </row>
-    <row r="94" spans="1:4">
+      <c r="E93" s="1">
+        <v>356.92</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5">
       <c r="A94" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C94" s="1">
         <v>250.55</v>
@@ -2245,10 +2533,13 @@
       <c r="D94" s="1">
         <v>130.45</v>
       </c>
-    </row>
-    <row r="95" spans="1:4">
+      <c r="E94" s="1">
+        <v>38.98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5">
       <c r="A95" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C95" s="1">
         <v>513.01</v>
@@ -2256,10 +2547,13 @@
       <c r="D95" s="1">
         <v>462.3600000000001</v>
       </c>
-    </row>
-    <row r="96" spans="1:4">
+      <c r="E95" s="1">
+        <v>458.36</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5">
       <c r="A96" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C96" s="1">
         <v>380.36</v>
@@ -2267,32 +2561,41 @@
       <c r="D96" s="1">
         <v>218.36</v>
       </c>
-    </row>
-    <row r="97" spans="1:4">
+      <c r="E96" s="1">
+        <v>143.37</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5">
       <c r="A97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C97" s="1">
         <v>563.5700000000001</v>
       </c>
       <c r="D97" s="1">
-        <v>401.92</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
+        <v>401.9200000000001</v>
+      </c>
+      <c r="E97" s="1">
+        <v>284.84</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5">
       <c r="A98" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C98" s="1">
         <v>315.21</v>
       </c>
       <c r="D98" s="1">
-        <v>509.3300000000002</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
+        <v>509.33</v>
+      </c>
+      <c r="E98" s="1">
+        <v>504.6100000000001</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5">
       <c r="A99" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C99" s="1">
         <v>377.75</v>
@@ -2300,10 +2603,13 @@
       <c r="D99" s="1">
         <v>165.97</v>
       </c>
-    </row>
-    <row r="100" spans="1:4">
+      <c r="E99" s="1">
+        <v>271.53</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5">
       <c r="A100" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C100" s="1">
         <v>315.04</v>
@@ -2311,10 +2617,13 @@
       <c r="D100" s="1">
         <v>105.67</v>
       </c>
-    </row>
-    <row r="101" spans="1:4">
+      <c r="E100" s="1">
+        <v>116.73</v>
+      </c>
+    </row>
+    <row r="101" spans="1:5">
       <c r="A101" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C101" s="1">
         <v>222.74</v>
@@ -2322,10 +2631,13 @@
       <c r="D101" s="1">
         <v>465.01</v>
       </c>
-    </row>
-    <row r="102" spans="1:4">
+      <c r="E101" s="1">
+        <v>165.81</v>
+      </c>
+    </row>
+    <row r="102" spans="1:5">
       <c r="A102" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C102" s="1">
         <v>159.77</v>
@@ -2333,10 +2645,13 @@
       <c r="D102" s="1">
         <v>198.55</v>
       </c>
-    </row>
-    <row r="103" spans="1:4">
+      <c r="E102" s="1">
+        <v>344.49</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5">
       <c r="A103" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C103" s="1">
         <v>293.92</v>
@@ -2344,10 +2659,13 @@
       <c r="D103" s="1">
         <v>179.56</v>
       </c>
-    </row>
-    <row r="104" spans="1:4">
+      <c r="E103" s="1">
+        <v>233.05</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5">
       <c r="A104" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C104" s="1">
         <v>175.04</v>
@@ -2355,10 +2673,13 @@
       <c r="D104" s="1">
         <v>173.91</v>
       </c>
-    </row>
-    <row r="105" spans="1:4">
+      <c r="E104" s="1">
+        <v>98.94</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5">
       <c r="A105" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C105" s="1">
         <v>130.86</v>
@@ -2366,10 +2687,13 @@
       <c r="D105" s="1">
         <v>106.6</v>
       </c>
-    </row>
-    <row r="106" spans="1:4">
+      <c r="E105" s="1">
+        <v>97.46000000000001</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5">
       <c r="A106" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C106" s="1">
         <v>147.76</v>
@@ -2377,10 +2701,13 @@
       <c r="D106" s="1">
         <v>45.62</v>
       </c>
-    </row>
-    <row r="107" spans="1:4">
+      <c r="E106" s="1">
+        <v>112.62</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5">
       <c r="A107" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C107" s="1">
         <v>420.72</v>
@@ -2388,10 +2715,13 @@
       <c r="D107" s="1">
         <v>219.93</v>
       </c>
-    </row>
-    <row r="108" spans="1:4">
+      <c r="E107" s="1">
+        <v>83.95999999999999</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5">
       <c r="A108" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C108" s="1">
         <v>300.91</v>
@@ -2399,10 +2729,13 @@
       <c r="D108" s="1">
         <v>74.28</v>
       </c>
-    </row>
-    <row r="109" spans="1:4">
+      <c r="E108" s="1">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="109" spans="1:5">
       <c r="A109" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C109" s="1">
         <v>225.04</v>
@@ -2410,21 +2743,27 @@
       <c r="D109" s="1">
         <v>179.65</v>
       </c>
-    </row>
-    <row r="110" spans="1:4">
+      <c r="E109" s="1">
+        <v>318.99</v>
+      </c>
+    </row>
+    <row r="110" spans="1:5">
       <c r="A110" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C110" s="1">
-        <v>95.59</v>
+        <v>95.58999999999999</v>
       </c>
       <c r="D110" s="1">
         <v>489.8200000000001</v>
       </c>
-    </row>
-    <row r="111" spans="1:4">
+      <c r="E110" s="1">
+        <v>133.05</v>
+      </c>
+    </row>
+    <row r="111" spans="1:5">
       <c r="A111" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C111" s="1">
         <v>172.28</v>
@@ -2432,10 +2771,13 @@
       <c r="D111" s="1">
         <v>308.89</v>
       </c>
-    </row>
-    <row r="112" spans="1:4">
+      <c r="E111" s="1">
+        <v>122.65</v>
+      </c>
+    </row>
+    <row r="112" spans="1:5">
       <c r="A112" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C112" s="1">
         <v>68.98</v>
@@ -2443,10 +2785,13 @@
       <c r="D112" s="1">
         <v>164.44</v>
       </c>
-    </row>
-    <row r="113" spans="1:4">
+      <c r="E112" s="1">
+        <v>162.73</v>
+      </c>
+    </row>
+    <row r="113" spans="1:5">
       <c r="A113" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C113" s="1">
         <v>75.97</v>
@@ -2454,10 +2799,13 @@
       <c r="D113" s="1">
         <v>194.86</v>
       </c>
-    </row>
-    <row r="114" spans="1:4">
+      <c r="E113" s="1">
+        <v>215.67</v>
+      </c>
+    </row>
+    <row r="114" spans="1:5">
       <c r="A114" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C114" s="1">
         <v>231.59</v>
@@ -2465,21 +2813,27 @@
       <c r="D114" s="1">
         <v>95.38999999999999</v>
       </c>
-    </row>
-    <row r="115" spans="1:4">
+      <c r="E114" s="1">
+        <v>404.89</v>
+      </c>
+    </row>
+    <row r="115" spans="1:5">
       <c r="A115" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D115" s="1">
         <v>26.99</v>
       </c>
-    </row>
-    <row r="116" spans="1:4">
+      <c r="E115" s="1">
+        <v>25.64</v>
+      </c>
+    </row>
+    <row r="116" spans="1:5">
       <c r="A116" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C116" s="1">
         <v>56.98</v>
@@ -2487,10 +2841,13 @@
       <c r="D116" s="1">
         <v>84.16</v>
       </c>
-    </row>
-    <row r="117" spans="1:4">
+      <c r="E116" s="1">
+        <v>354.68</v>
+      </c>
+    </row>
+    <row r="117" spans="1:5">
       <c r="A117" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C117" s="1">
         <v>110.46</v>
@@ -2498,10 +2855,13 @@
       <c r="D117" s="1">
         <v>88.97</v>
       </c>
-    </row>
-    <row r="118" spans="1:4">
+      <c r="E117" s="1">
+        <v>97.31</v>
+      </c>
+    </row>
+    <row r="118" spans="1:5">
       <c r="A118" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C118" s="1">
         <v>284</v>
@@ -2509,10 +2869,13 @@
       <c r="D118" s="1">
         <v>112.95</v>
       </c>
-    </row>
-    <row r="119" spans="1:4">
+      <c r="E118" s="1">
+        <v>129.68</v>
+      </c>
+    </row>
+    <row r="119" spans="1:5">
       <c r="A119" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C119" s="1">
         <v>117.15</v>
@@ -2520,21 +2883,27 @@
       <c r="D119" s="1">
         <v>91.97999999999999</v>
       </c>
-    </row>
-    <row r="120" spans="1:4">
+      <c r="E119" s="1">
+        <v>80.97</v>
+      </c>
+    </row>
+    <row r="120" spans="1:5">
       <c r="A120" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C120" s="1">
         <v>543.2</v>
       </c>
       <c r="D120" s="1">
-        <v>824.48</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
+        <v>824.4800000000001</v>
+      </c>
+      <c r="E120" s="1">
+        <v>732.8900000000001</v>
+      </c>
+    </row>
+    <row r="121" spans="1:5">
       <c r="A121" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C121" s="1">
         <v>96.97</v>
@@ -2542,10 +2911,13 @@
       <c r="D121" s="1">
         <v>111.97</v>
       </c>
-    </row>
-    <row r="122" spans="1:4">
+      <c r="E121" s="1">
+        <v>202.94</v>
+      </c>
+    </row>
+    <row r="122" spans="1:5">
       <c r="A122" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C122" s="1">
         <v>252.51</v>
@@ -2553,10 +2925,13 @@
       <c r="D122" s="1">
         <v>298.2</v>
       </c>
-    </row>
-    <row r="123" spans="1:4">
+      <c r="E122" s="1">
+        <v>208.92</v>
+      </c>
+    </row>
+    <row r="123" spans="1:5">
       <c r="A123" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C123" s="1">
         <v>108.77</v>
@@ -2564,10 +2939,13 @@
       <c r="D123" s="1">
         <v>155.43</v>
       </c>
-    </row>
-    <row r="124" spans="1:4">
+      <c r="E123" s="1">
+        <v>180.79</v>
+      </c>
+    </row>
+    <row r="124" spans="1:5">
       <c r="A124" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C124" s="1">
         <v>237.35</v>
@@ -2575,10 +2953,13 @@
       <c r="D124" s="1">
         <v>103.52</v>
       </c>
-    </row>
-    <row r="125" spans="1:4">
+      <c r="E124" s="1">
+        <v>145.47</v>
+      </c>
+    </row>
+    <row r="125" spans="1:5">
       <c r="A125" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C125" s="1">
         <v>163.33</v>
@@ -2586,10 +2967,13 @@
       <c r="D125" s="1">
         <v>98.67</v>
       </c>
-    </row>
-    <row r="126" spans="1:4">
+      <c r="E125" s="1">
+        <v>255.0500000000001</v>
+      </c>
+    </row>
+    <row r="126" spans="1:5">
       <c r="A126" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C126" s="1">
         <v>59.98</v>
@@ -2597,10 +2981,13 @@
       <c r="D126" s="1">
         <v>109.3</v>
       </c>
-    </row>
-    <row r="127" spans="1:4">
+      <c r="E126" s="1">
+        <v>153.09</v>
+      </c>
+    </row>
+    <row r="127" spans="1:5">
       <c r="A127" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C127" s="1">
         <v>310.1</v>
@@ -2608,10 +2995,13 @@
       <c r="D127" s="1">
         <v>422.75</v>
       </c>
-    </row>
-    <row r="128" spans="1:4">
+      <c r="E127" s="1">
+        <v>296.53</v>
+      </c>
+    </row>
+    <row r="128" spans="1:5">
       <c r="A128" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C128" s="1">
         <v>115.08</v>
@@ -2619,21 +3009,27 @@
       <c r="D128" s="1">
         <v>242.89</v>
       </c>
-    </row>
-    <row r="129" spans="1:4">
+      <c r="E128" s="1">
+        <v>264.79</v>
+      </c>
+    </row>
+    <row r="129" spans="1:5">
       <c r="A129" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C129" s="1">
         <v>177.81</v>
       </c>
       <c r="D129" s="1">
-        <v>80.37</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
+        <v>80.36999999999999</v>
+      </c>
+      <c r="E129" s="1">
+        <v>137.96</v>
+      </c>
+    </row>
+    <row r="130" spans="1:5">
       <c r="A130" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C130" s="1">
         <v>367.1900000000001</v>
@@ -2641,21 +3037,27 @@
       <c r="D130" s="1">
         <v>219.99</v>
       </c>
-    </row>
-    <row r="131" spans="1:4">
+      <c r="E130" s="1">
+        <v>365.2200000000001</v>
+      </c>
+    </row>
+    <row r="131" spans="1:5">
       <c r="A131" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C131" s="1">
         <v>170.96</v>
       </c>
       <c r="D131" s="1">
-        <v>479.86</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
+        <v>479.8600000000001</v>
+      </c>
+      <c r="E131" s="1">
+        <v>322.6000000000001</v>
+      </c>
+    </row>
+    <row r="132" spans="1:5">
       <c r="A132" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C132" s="1">
         <v>16.3</v>
@@ -2663,10 +3065,13 @@
       <c r="D132" s="1">
         <v>14.39</v>
       </c>
-    </row>
-    <row r="133" spans="1:4">
+      <c r="E132" s="1">
+        <v>41.48</v>
+      </c>
+    </row>
+    <row r="133" spans="1:5">
       <c r="A133" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C133" s="1">
         <v>169.15</v>
@@ -2674,10 +3079,13 @@
       <c r="D133" s="1">
         <v>208.83</v>
       </c>
-    </row>
-    <row r="134" spans="1:4">
+      <c r="E133" s="1">
+        <v>516.4300000000001</v>
+      </c>
+    </row>
+    <row r="134" spans="1:5">
       <c r="A134" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C134" s="1">
         <v>481.06</v>
@@ -2685,10 +3093,13 @@
       <c r="D134" s="1">
         <v>336</v>
       </c>
-    </row>
-    <row r="135" spans="1:4">
+      <c r="E134" s="1">
+        <v>284.05</v>
+      </c>
+    </row>
+    <row r="135" spans="1:5">
       <c r="A135" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C135" s="1">
         <v>254.07</v>
@@ -2696,21 +3107,27 @@
       <c r="D135" s="1">
         <v>247.91</v>
       </c>
-    </row>
-    <row r="136" spans="1:4">
+      <c r="E135" s="1">
+        <v>190.98</v>
+      </c>
+    </row>
+    <row r="136" spans="1:5">
       <c r="A136" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C136" s="1">
         <v>226.01</v>
       </c>
       <c r="D136" s="1">
-        <v>114.97</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
+        <v>143.96</v>
+      </c>
+      <c r="E136" s="1">
+        <v>540.35</v>
+      </c>
+    </row>
+    <row r="137" spans="1:5">
       <c r="A137" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C137" s="1">
         <v>119.57</v>
@@ -2718,21 +3135,27 @@
       <c r="D137" s="1">
         <v>161.04</v>
       </c>
-    </row>
-    <row r="138" spans="1:4">
+      <c r="E137" s="1">
+        <v>92.06999999999999</v>
+      </c>
+    </row>
+    <row r="138" spans="1:5">
       <c r="A138" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C138" s="1">
-        <v>457.3600000000001</v>
+        <v>457.36</v>
       </c>
       <c r="D138" s="1">
         <v>350.99</v>
       </c>
-    </row>
-    <row r="139" spans="1:4">
+      <c r="E138" s="1">
+        <v>212.86</v>
+      </c>
+    </row>
+    <row r="139" spans="1:5">
       <c r="A139" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C139" s="1">
         <v>352.86</v>
@@ -2740,21 +3163,27 @@
       <c r="D139" s="1">
         <v>267.81</v>
       </c>
-    </row>
-    <row r="140" spans="1:4">
+      <c r="E139" s="1">
+        <v>194.94</v>
+      </c>
+    </row>
+    <row r="140" spans="1:5">
       <c r="A140" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C140" s="1">
-        <v>423.87</v>
+        <v>423.8700000000001</v>
       </c>
       <c r="D140" s="1">
         <v>172.94</v>
       </c>
-    </row>
-    <row r="141" spans="1:4">
+      <c r="E140" s="1">
+        <v>235.2</v>
+      </c>
+    </row>
+    <row r="141" spans="1:5">
       <c r="A141" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C141" s="1">
         <v>778.97</v>
@@ -2762,21 +3191,27 @@
       <c r="D141" s="1">
         <v>438.23</v>
       </c>
-    </row>
-    <row r="142" spans="1:4">
+      <c r="E141" s="1">
+        <v>328.53</v>
+      </c>
+    </row>
+    <row r="142" spans="1:5">
       <c r="A142" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C142" s="1">
         <v>174.39</v>
       </c>
       <c r="D142" s="1">
-        <v>438.3100000000001</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
+        <v>438.31</v>
+      </c>
+      <c r="E142" s="1">
+        <v>542.02</v>
+      </c>
+    </row>
+    <row r="143" spans="1:5">
       <c r="A143" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C143" s="1">
         <v>96.95999999999999</v>
@@ -2784,21 +3219,27 @@
       <c r="D143" s="1">
         <v>171.46</v>
       </c>
-    </row>
-    <row r="144" spans="1:4">
+      <c r="E143" s="1">
+        <v>365.7300000000001</v>
+      </c>
+    </row>
+    <row r="144" spans="1:5">
       <c r="A144" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C144" s="1">
-        <v>98.06</v>
+        <v>98.05999999999999</v>
       </c>
       <c r="D144" s="1">
         <v>119.46</v>
       </c>
-    </row>
-    <row r="145" spans="1:4">
+      <c r="E144" s="1">
+        <v>65.98</v>
+      </c>
+    </row>
+    <row r="145" spans="1:5">
       <c r="A145" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C145" s="1">
         <v>154.72</v>
@@ -2806,10 +3247,13 @@
       <c r="D145" s="1">
         <v>204.32</v>
       </c>
-    </row>
-    <row r="146" spans="1:4">
+      <c r="E145" s="1">
+        <v>109.96</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5">
       <c r="A146" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C146" s="1">
         <v>81.95999999999999</v>
@@ -2817,10 +3261,13 @@
       <c r="D146" s="1">
         <v>59.98</v>
       </c>
-    </row>
-    <row r="147" spans="1:4">
+      <c r="E146" s="1">
+        <v>289.49</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5">
       <c r="A147" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C147" s="1">
         <v>271.77</v>
@@ -2828,21 +3275,27 @@
       <c r="D147" s="1">
         <v>156.74</v>
       </c>
-    </row>
-    <row r="148" spans="1:4">
+      <c r="E147" s="1">
+        <v>104.96</v>
+      </c>
+    </row>
+    <row r="148" spans="1:5">
       <c r="A148" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C148" s="1">
-        <v>422.8500000000001</v>
+        <v>422.85</v>
       </c>
       <c r="D148" s="1">
-        <v>343.3100000000001</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
+        <v>343.31</v>
+      </c>
+      <c r="E148" s="1">
+        <v>72.97</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5">
       <c r="A149" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C149" s="1">
         <v>107.17</v>
@@ -2850,32 +3303,41 @@
       <c r="D149" s="1">
         <v>303.72</v>
       </c>
-    </row>
-    <row r="150" spans="1:4">
+      <c r="E149" s="1">
+        <v>433.4000000000001</v>
+      </c>
+    </row>
+    <row r="150" spans="1:5">
       <c r="A150" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C150" s="1">
         <v>393.96</v>
       </c>
       <c r="D150" s="1">
-        <v>738.9699999999999</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
+        <v>738.97</v>
+      </c>
+      <c r="E150" s="1">
+        <v>492.5400000000001</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5">
       <c r="A151" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C151" s="1">
-        <v>70.38</v>
+        <v>70.38000000000001</v>
       </c>
       <c r="D151" s="1">
         <v>14.99</v>
       </c>
-    </row>
-    <row r="152" spans="1:4">
+      <c r="E151" s="1">
+        <v>52.48999999999999</v>
+      </c>
+    </row>
+    <row r="152" spans="1:5">
       <c r="A152" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C152" s="1">
         <v>129.07</v>
@@ -2883,10 +3345,13 @@
       <c r="D152" s="1">
         <v>396.37</v>
       </c>
-    </row>
-    <row r="153" spans="1:4">
+      <c r="E152" s="1">
+        <v>266.53</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5">
       <c r="A153" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C153" s="1">
         <v>190.06</v>
@@ -2894,21 +3359,27 @@
       <c r="D153" s="1">
         <v>292.72</v>
       </c>
-    </row>
-    <row r="154" spans="1:4">
+      <c r="E153" s="1">
+        <v>150.18</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5">
       <c r="A154" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C154" s="1">
         <v>150.52</v>
       </c>
       <c r="D154" s="1">
-        <v>290.87</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
+        <v>290.8699999999999</v>
+      </c>
+      <c r="E154" s="1">
+        <v>262.7</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5">
       <c r="A155" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C155" s="1">
         <v>297.71</v>
@@ -2916,10 +3387,13 @@
       <c r="D155" s="1">
         <v>315.99</v>
       </c>
-    </row>
-    <row r="156" spans="1:4">
+      <c r="E155" s="1">
+        <v>240.91</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5">
       <c r="A156" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C156" s="1">
         <v>213.04</v>
@@ -2927,10 +3401,13 @@
       <c r="D156" s="1">
         <v>517.8100000000001</v>
       </c>
-    </row>
-    <row r="157" spans="1:4">
+      <c r="E156" s="1">
+        <v>648.39</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5">
       <c r="A157" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C157" s="1">
         <v>224.93</v>
@@ -2938,10 +3415,13 @@
       <c r="D157" s="1">
         <v>189.27</v>
       </c>
-    </row>
-    <row r="158" spans="1:4">
+      <c r="E157" s="1">
+        <v>315.46</v>
+      </c>
+    </row>
+    <row r="158" spans="1:5">
       <c r="A158" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C158" s="1">
         <v>466.91</v>
@@ -2949,10 +3429,13 @@
       <c r="D158" s="1">
         <v>180.16</v>
       </c>
-    </row>
-    <row r="159" spans="1:4">
+      <c r="E158" s="1">
+        <v>473.01</v>
+      </c>
+    </row>
+    <row r="159" spans="1:5">
       <c r="A159" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C159" s="1">
         <v>275.35</v>
@@ -2960,21 +3443,27 @@
       <c r="D159" s="1">
         <v>237.93</v>
       </c>
-    </row>
-    <row r="160" spans="1:4">
+      <c r="E159" s="1">
+        <v>191.14</v>
+      </c>
+    </row>
+    <row r="160" spans="1:5">
       <c r="A160" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C160" s="1">
-        <v>419.6700000000001</v>
+        <v>419.67</v>
       </c>
       <c r="D160" s="1">
         <v>298.96</v>
       </c>
-    </row>
-    <row r="161" spans="1:4">
+      <c r="E160" s="1">
+        <v>169.56</v>
+      </c>
+    </row>
+    <row r="161" spans="1:5">
       <c r="A161" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C161" s="1">
         <v>387.75</v>
@@ -2982,10 +3471,13 @@
       <c r="D161" s="1">
         <v>247.37</v>
       </c>
-    </row>
-    <row r="162" spans="1:4">
+      <c r="E161" s="1">
+        <v>413.61</v>
+      </c>
+    </row>
+    <row r="162" spans="1:5">
       <c r="A162" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C162" s="1">
         <v>69.97</v>
@@ -2993,10 +3485,13 @@
       <c r="D162" s="1">
         <v>274.14</v>
       </c>
-    </row>
-    <row r="163" spans="1:4">
+      <c r="E162" s="1">
+        <v>197.37</v>
+      </c>
+    </row>
+    <row r="163" spans="1:5">
       <c r="A163" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C163" s="1">
         <v>68.08</v>
@@ -3004,10 +3499,13 @@
       <c r="D163" s="1">
         <v>195.72</v>
       </c>
-    </row>
-    <row r="164" spans="1:4">
+      <c r="E163" s="1">
+        <v>110.06</v>
+      </c>
+    </row>
+    <row r="164" spans="1:5">
       <c r="A164" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C164" s="1">
         <v>141.95</v>
@@ -3015,10 +3513,13 @@
       <c r="D164" s="1">
         <v>173.25</v>
       </c>
-    </row>
-    <row r="165" spans="1:4">
+      <c r="E164" s="1">
+        <v>197.27</v>
+      </c>
+    </row>
+    <row r="165" spans="1:5">
       <c r="A165" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C165" s="1">
         <v>76.86999999999999</v>
@@ -3026,10 +3527,13 @@
       <c r="D165" s="1">
         <v>146.13</v>
       </c>
-    </row>
-    <row r="166" spans="1:4">
+      <c r="E165" s="1">
+        <v>140.32</v>
+      </c>
+    </row>
+    <row r="166" spans="1:5">
       <c r="A166" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C166" s="1">
         <v>68.77</v>
@@ -3037,10 +3541,13 @@
       <c r="D166" s="1">
         <v>239.59</v>
       </c>
-    </row>
-    <row r="167" spans="1:4">
+      <c r="E166" s="1">
+        <v>401.77</v>
+      </c>
+    </row>
+    <row r="167" spans="1:5">
       <c r="A167" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C167" s="1">
         <v>240.25</v>
@@ -3048,10 +3555,13 @@
       <c r="D167" s="1">
         <v>124.75</v>
       </c>
-    </row>
-    <row r="168" spans="1:4">
+      <c r="E167" s="1">
+        <v>69.98</v>
+      </c>
+    </row>
+    <row r="168" spans="1:5">
       <c r="A168" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C168" s="1">
         <v>584.5700000000001</v>
@@ -3059,10 +3569,13 @@
       <c r="D168" s="1">
         <v>1062.09</v>
       </c>
-    </row>
-    <row r="169" spans="1:4">
+      <c r="E168" s="1">
+        <v>1208.31</v>
+      </c>
+    </row>
+    <row r="169" spans="1:5">
       <c r="A169" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C169" s="1">
         <v>25.99</v>
@@ -3070,10 +3583,13 @@
       <c r="D169" s="1">
         <v>100.57</v>
       </c>
-    </row>
-    <row r="170" spans="1:4">
+      <c r="E169" s="1">
+        <v>122.67</v>
+      </c>
+    </row>
+    <row r="170" spans="1:5">
       <c r="A170" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C170" s="1">
         <v>543.8100000000001</v>
@@ -3081,10 +3597,13 @@
       <c r="D170" s="1">
         <v>1119.39</v>
       </c>
-    </row>
-    <row r="171" spans="1:4">
+      <c r="E170" s="1">
+        <v>874.24</v>
+      </c>
+    </row>
+    <row r="171" spans="1:5">
       <c r="A171" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C171" s="1">
         <v>147.29</v>
@@ -3092,10 +3611,13 @@
       <c r="D171" s="1">
         <v>257.94</v>
       </c>
-    </row>
-    <row r="172" spans="1:4">
+      <c r="E171" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="172" spans="1:5">
       <c r="A172" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C172" s="1">
         <v>350.1800000000001</v>
@@ -3103,10 +3625,13 @@
       <c r="D172" s="1">
         <v>291.92</v>
       </c>
-    </row>
-    <row r="173" spans="1:4">
+      <c r="E172" s="1">
+        <v>363.6100000000001</v>
+      </c>
+    </row>
+    <row r="173" spans="1:5">
       <c r="A173" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C173" s="1">
         <v>352.58</v>
@@ -3114,10 +3639,13 @@
       <c r="D173" s="1">
         <v>333.21</v>
       </c>
-    </row>
-    <row r="174" spans="1:4">
+      <c r="E173" s="1">
+        <v>324.9000000000001</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5">
       <c r="A174" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C174" s="1">
         <v>336.89</v>
@@ -3125,10 +3653,13 @@
       <c r="D174" s="1">
         <v>248.91</v>
       </c>
-    </row>
-    <row r="175" spans="1:4">
+      <c r="E174" s="1">
+        <v>224.94</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5">
       <c r="A175" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C175" s="1">
         <v>361.73</v>
@@ -3136,10 +3667,13 @@
       <c r="D175" s="1">
         <v>75.90000000000001</v>
       </c>
-    </row>
-    <row r="176" spans="1:4">
+      <c r="E175" s="1">
+        <v>166.52</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5">
       <c r="A176" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C176" s="1">
         <v>234.52</v>
@@ -3147,10 +3681,13 @@
       <c r="D176" s="1">
         <v>191.18</v>
       </c>
-    </row>
-    <row r="177" spans="1:4">
+      <c r="E176" s="1">
+        <v>400.7</v>
+      </c>
+    </row>
+    <row r="177" spans="1:5">
       <c r="A177" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C177" s="1">
         <v>99.94999999999999</v>
@@ -3158,10 +3695,13 @@
       <c r="D177" s="1">
         <v>57.99</v>
       </c>
-    </row>
-    <row r="178" spans="1:4">
+      <c r="E177" s="1">
+        <v>181.54</v>
+      </c>
+    </row>
+    <row r="178" spans="1:5">
       <c r="A178" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C178" s="1">
         <v>160.93</v>
@@ -3169,10 +3709,13 @@
       <c r="D178" s="1">
         <v>77.17</v>
       </c>
-    </row>
-    <row r="179" spans="1:4">
+      <c r="E178" s="1">
+        <v>57.95</v>
+      </c>
+    </row>
+    <row r="179" spans="1:5">
       <c r="A179" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C179" s="1">
         <v>96.97</v>
@@ -3180,10 +3723,13 @@
       <c r="D179" s="1">
         <v>318.34</v>
       </c>
-    </row>
-    <row r="180" spans="1:4">
+      <c r="E179" s="1">
+        <v>18.99</v>
+      </c>
+    </row>
+    <row r="180" spans="1:5">
       <c r="A180" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C180" s="1">
         <v>26.99</v>
@@ -3191,32 +3737,41 @@
       <c r="D180" s="1">
         <v>104.56</v>
       </c>
-    </row>
-    <row r="181" spans="1:4">
+      <c r="E180" s="1">
+        <v>54.47</v>
+      </c>
+    </row>
+    <row r="181" spans="1:5">
       <c r="A181" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C181" s="1">
         <v>144.73</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
+        <v>43</v>
+      </c>
+      <c r="E181" s="1">
+        <v>67.19</v>
+      </c>
+    </row>
+    <row r="182" spans="1:5">
       <c r="A182" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C182" s="1">
         <v>118.44</v>
       </c>
       <c r="D182" s="1">
-        <v>418.62</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
+        <v>447.61</v>
+      </c>
+      <c r="E182" s="1">
+        <v>110.96</v>
+      </c>
+    </row>
+    <row r="183" spans="1:5">
       <c r="A183" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C183" s="1">
         <v>59.98</v>
@@ -3224,10 +3779,13 @@
       <c r="D183" s="1">
         <v>111.37</v>
       </c>
-    </row>
-    <row r="184" spans="1:4">
+      <c r="E183" s="1">
+        <v>82.55000000000001</v>
+      </c>
+    </row>
+    <row r="184" spans="1:5">
       <c r="A184" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C184" s="1">
         <v>35.78</v>
@@ -3235,21 +3793,27 @@
       <c r="D184" s="1">
         <v>303.67</v>
       </c>
-    </row>
-    <row r="185" spans="1:4">
+      <c r="E184" s="1">
+        <v>128.95</v>
+      </c>
+    </row>
+    <row r="185" spans="1:5">
       <c r="A185" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C185" s="1">
         <v>389.27</v>
       </c>
       <c r="D185" s="1">
-        <v>342.6799999999999</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
+        <v>342.68</v>
+      </c>
+      <c r="E185" s="1">
+        <v>448.0300000000001</v>
+      </c>
+    </row>
+    <row r="186" spans="1:5">
       <c r="A186" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C186" s="1">
         <v>394.71</v>
@@ -3257,10 +3821,13 @@
       <c r="D186" s="1">
         <v>691.3799999999999</v>
       </c>
-    </row>
-    <row r="187" spans="1:4">
+      <c r="E186" s="1">
+        <v>643.6799999999999</v>
+      </c>
+    </row>
+    <row r="187" spans="1:5">
       <c r="A187" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C187" s="1">
         <v>254.11</v>
@@ -3268,10 +3835,13 @@
       <c r="D187" s="1">
         <v>127.96</v>
       </c>
-    </row>
-    <row r="188" spans="1:4">
+      <c r="E187" s="1">
+        <v>230.94</v>
+      </c>
+    </row>
+    <row r="188" spans="1:5">
       <c r="A188" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C188" s="1">
         <v>94.95999999999999</v>
@@ -3279,21 +3849,27 @@
       <c r="D188" s="1">
         <v>121.18</v>
       </c>
-    </row>
-    <row r="189" spans="1:4">
+      <c r="E188" s="1">
+        <v>93.65000000000001</v>
+      </c>
+    </row>
+    <row r="189" spans="1:5">
       <c r="A189" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C189" s="1">
-        <v>987.5599999999999</v>
+        <v>987.5600000000002</v>
       </c>
       <c r="D189" s="1">
         <v>754.75</v>
       </c>
-    </row>
-    <row r="190" spans="1:4">
+      <c r="E189" s="1">
+        <v>772.5900000000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:5">
       <c r="A190" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C190" s="1">
         <v>152.11</v>
@@ -3301,10 +3877,13 @@
       <c r="D190" s="1">
         <v>208.42</v>
       </c>
-    </row>
-    <row r="191" spans="1:4">
+      <c r="E190" s="1">
+        <v>169.7</v>
+      </c>
+    </row>
+    <row r="191" spans="1:5">
       <c r="A191" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C191" s="1">
         <v>129.45</v>
@@ -3312,10 +3891,13 @@
       <c r="D191" s="1">
         <v>178.74</v>
       </c>
-    </row>
-    <row r="192" spans="1:4">
+      <c r="E191" s="1">
+        <v>89.75999999999999</v>
+      </c>
+    </row>
+    <row r="192" spans="1:5">
       <c r="A192" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C192" s="1">
         <v>143</v>
@@ -3323,10 +3905,13 @@
       <c r="D192" s="1">
         <v>270.4</v>
       </c>
-    </row>
-    <row r="193" spans="1:4">
+      <c r="E192" s="1">
+        <v>102.34</v>
+      </c>
+    </row>
+    <row r="193" spans="1:5">
       <c r="A193" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C193" s="1">
         <v>363.3200000000001</v>
@@ -3334,43 +3919,55 @@
       <c r="D193" s="1">
         <v>92.95999999999999</v>
       </c>
-    </row>
-    <row r="194" spans="1:4">
+      <c r="E193" s="1">
+        <v>429.08</v>
+      </c>
+    </row>
+    <row r="194" spans="1:5">
       <c r="A194" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C194" s="1">
         <v>178.18</v>
       </c>
       <c r="D194" s="1">
-        <v>681.7299999999999</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
+        <v>681.73</v>
+      </c>
+      <c r="E194" s="1">
+        <v>364.42</v>
+      </c>
+    </row>
+    <row r="195" spans="1:5">
       <c r="A195" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C195" s="1">
-        <v>613.98</v>
+        <v>613.9800000000001</v>
       </c>
       <c r="D195" s="1">
         <v>1082.1</v>
       </c>
-    </row>
-    <row r="196" spans="1:4">
+      <c r="E195" s="1">
+        <v>552.5</v>
+      </c>
+    </row>
+    <row r="196" spans="1:5">
       <c r="A196" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C196" s="1">
-        <v>501.0100000000001</v>
+        <v>501.01</v>
       </c>
       <c r="D196" s="1">
         <v>82.09</v>
       </c>
-    </row>
-    <row r="197" spans="1:4">
+      <c r="E196" s="1">
+        <v>274.52</v>
+      </c>
+    </row>
+    <row r="197" spans="1:5">
       <c r="A197" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C197" s="1">
         <v>21.99</v>
@@ -3378,21 +3975,27 @@
       <c r="D197" s="1">
         <v>205.28</v>
       </c>
-    </row>
-    <row r="198" spans="1:4">
+      <c r="E197" s="1">
+        <v>170.35</v>
+      </c>
+    </row>
+    <row r="198" spans="1:5">
       <c r="A198" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C198" s="1">
-        <v>391.98</v>
+        <v>391.9800000000001</v>
       </c>
       <c r="D198" s="1">
         <v>432.87</v>
       </c>
-    </row>
-    <row r="199" spans="1:4">
+      <c r="E198" s="1">
+        <v>724.8799999999999</v>
+      </c>
+    </row>
+    <row r="199" spans="1:5">
       <c r="A199" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C199" s="1">
         <v>540.11</v>
@@ -3400,21 +4003,27 @@
       <c r="D199" s="1">
         <v>485.52</v>
       </c>
-    </row>
-    <row r="200" spans="1:4">
+      <c r="E199" s="1">
+        <v>581.6200000000001</v>
+      </c>
+    </row>
+    <row r="200" spans="1:5">
       <c r="A200" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C200" s="1">
         <v>104.46</v>
       </c>
       <c r="D200" s="1">
-        <v>94.67000000000002</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
+        <v>94.67</v>
+      </c>
+      <c r="E200" s="1">
+        <v>55.98</v>
+      </c>
+    </row>
+    <row r="201" spans="1:5">
       <c r="A201" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="C201" s="1">
         <v>144.05</v>
@@ -3422,21 +4031,27 @@
       <c r="D201" s="1">
         <v>85.97</v>
       </c>
-    </row>
-    <row r="202" spans="1:4">
+      <c r="E201" s="1">
+        <v>78.95999999999999</v>
+      </c>
+    </row>
+    <row r="202" spans="1:5">
       <c r="A202" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="C202" s="1">
         <v>1270.01</v>
       </c>
       <c r="D202" s="1">
-        <v>1159.52</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
+        <v>1235.5</v>
+      </c>
+      <c r="E202" s="1">
+        <v>118.28</v>
+      </c>
+    </row>
+    <row r="203" spans="1:5">
       <c r="A203" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="C203" s="1">
         <v>373.34</v>
@@ -3444,10 +4059,13 @@
       <c r="D203" s="1">
         <v>527.59</v>
       </c>
-    </row>
-    <row r="204" spans="1:4">
+      <c r="E203" s="1">
+        <v>395.1800000000001</v>
+      </c>
+    </row>
+    <row r="204" spans="1:5">
       <c r="A204" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="C204" s="1">
         <v>151.95</v>
@@ -3455,21 +4073,27 @@
       <c r="D204" s="1">
         <v>106.58</v>
       </c>
-    </row>
-    <row r="205" spans="1:4">
+      <c r="E204" s="1">
+        <v>245.12</v>
+      </c>
+    </row>
+    <row r="205" spans="1:5">
       <c r="A205" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C205" s="1">
         <v>82.64999999999999</v>
       </c>
       <c r="D205" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
+        <v>43</v>
+      </c>
+      <c r="E205" s="1">
+        <v>71.53999999999999</v>
+      </c>
+    </row>
+    <row r="206" spans="1:5">
       <c r="A206" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C206" s="1">
         <v>42.56</v>
@@ -3477,10 +4101,13 @@
       <c r="D206" s="1">
         <v>112.26</v>
       </c>
-    </row>
-    <row r="207" spans="1:4">
+      <c r="E206" s="1">
+        <v>87.95999999999999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:5">
       <c r="A207" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="C207" s="1">
         <v>222.17</v>
@@ -3488,10 +4115,13 @@
       <c r="D207" s="1">
         <v>224.15</v>
       </c>
-    </row>
-    <row r="208" spans="1:4">
+      <c r="E207" s="1">
+        <v>160.87</v>
+      </c>
+    </row>
+    <row r="208" spans="1:5">
       <c r="A208" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C208" s="1">
         <v>165.73</v>
@@ -3499,10 +4129,13 @@
       <c r="D208" s="1">
         <v>94.25999999999999</v>
       </c>
-    </row>
-    <row r="209" spans="1:4">
+      <c r="E208" s="1">
+        <v>147.25</v>
+      </c>
+    </row>
+    <row r="209" spans="1:5">
       <c r="A209" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C209" s="1">
         <v>122.42</v>
@@ -3510,10 +4143,13 @@
       <c r="D209" s="1">
         <v>178.96</v>
       </c>
-    </row>
-    <row r="210" spans="1:4">
+      <c r="E209" s="1">
+        <v>71.98</v>
+      </c>
+    </row>
+    <row r="210" spans="1:5">
       <c r="A210" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C210" s="1">
         <v>65.27</v>
@@ -3521,10 +4157,13 @@
       <c r="D210" s="1">
         <v>104.77</v>
       </c>
-    </row>
-    <row r="211" spans="1:4">
+      <c r="E210" s="1">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="211" spans="1:5">
       <c r="A211" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C211" s="1">
         <v>135.74</v>
@@ -3532,10 +4171,13 @@
       <c r="D211" s="1">
         <v>61.97</v>
       </c>
-    </row>
-    <row r="212" spans="1:4">
+      <c r="E211" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="212" spans="1:5">
       <c r="A212" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C212" s="1">
         <v>143.95</v>
@@ -3543,10 +4185,13 @@
       <c r="D212" s="1">
         <v>106.77</v>
       </c>
-    </row>
-    <row r="213" spans="1:4">
+      <c r="E212" s="1">
+        <v>127.96</v>
+      </c>
+    </row>
+    <row r="213" spans="1:5">
       <c r="A213" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C213" s="1">
         <v>245.33</v>
@@ -3554,10 +4199,13 @@
       <c r="D213" s="1">
         <v>148.36</v>
       </c>
-    </row>
-    <row r="214" spans="1:4">
+      <c r="E213" s="1">
+        <v>265.12</v>
+      </c>
+    </row>
+    <row r="214" spans="1:5">
       <c r="A214" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C214" s="1">
         <v>171.54</v>
@@ -3565,10 +4213,13 @@
       <c r="D214" s="1">
         <v>47.98</v>
       </c>
-    </row>
-    <row r="215" spans="1:4">
+      <c r="E214" s="1">
+        <v>159.44</v>
+      </c>
+    </row>
+    <row r="215" spans="1:5">
       <c r="A215" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C215" s="1">
         <v>181.37</v>
@@ -3576,10 +4227,13 @@
       <c r="D215" s="1">
         <v>16.49</v>
       </c>
-    </row>
-    <row r="216" spans="1:4">
+      <c r="E215" s="1">
+        <v>42.98</v>
+      </c>
+    </row>
+    <row r="216" spans="1:5">
       <c r="A216" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C216" s="1">
         <v>187.33</v>
@@ -3587,10 +4241,13 @@
       <c r="D216" s="1">
         <v>129.07</v>
       </c>
-    </row>
-    <row r="217" spans="1:4">
+      <c r="E216" s="1">
+        <v>127.95</v>
+      </c>
+    </row>
+    <row r="217" spans="1:5">
       <c r="A217" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C217" s="1">
         <v>181.93</v>
@@ -3598,10 +4255,13 @@
       <c r="D217" s="1">
         <v>152.03</v>
       </c>
-    </row>
-    <row r="218" spans="1:4">
+      <c r="E217" s="1">
+        <v>78.2</v>
+      </c>
+    </row>
+    <row r="218" spans="1:5">
       <c r="A218" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C218" s="1">
         <v>47.28</v>
@@ -3609,10 +4269,13 @@
       <c r="D218" s="1">
         <v>248.83</v>
       </c>
-    </row>
-    <row r="219" spans="1:4">
+      <c r="E218" s="1">
+        <v>36.28</v>
+      </c>
+    </row>
+    <row r="219" spans="1:5">
       <c r="A219" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C219" s="1">
         <v>187.95</v>
@@ -3620,10 +4283,13 @@
       <c r="D219" s="1">
         <v>202.42</v>
       </c>
-    </row>
-    <row r="220" spans="1:4">
+      <c r="E219" s="1">
+        <v>191.22</v>
+      </c>
+    </row>
+    <row r="220" spans="1:5">
       <c r="A220" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C220" s="1">
         <v>196.84</v>
@@ -3631,10 +4297,13 @@
       <c r="D220" s="1">
         <v>242.23</v>
       </c>
-    </row>
-    <row r="221" spans="1:4">
+      <c r="E220" s="1">
+        <v>255.93</v>
+      </c>
+    </row>
+    <row r="221" spans="1:5">
       <c r="A221" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C221" s="1">
         <v>225.41</v>
@@ -3642,10 +4311,13 @@
       <c r="D221" s="1">
         <v>145.95</v>
       </c>
-    </row>
-    <row r="222" spans="1:4">
+      <c r="E221" s="1">
+        <v>244.2</v>
+      </c>
+    </row>
+    <row r="222" spans="1:5">
       <c r="A222" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C222" s="1">
         <v>214.89</v>
@@ -3653,10 +4325,13 @@
       <c r="D222" s="1">
         <v>161.15</v>
       </c>
-    </row>
-    <row r="223" spans="1:4">
+      <c r="E222" s="1">
+        <v>21.99</v>
+      </c>
+    </row>
+    <row r="223" spans="1:5">
       <c r="A223" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C223" s="1">
         <v>529.5600000000001</v>
@@ -3664,10 +4339,13 @@
       <c r="D223" s="1">
         <v>289.69</v>
       </c>
-    </row>
-    <row r="224" spans="1:4">
+      <c r="E223" s="1">
+        <v>536.9400000000001</v>
+      </c>
+    </row>
+    <row r="224" spans="1:5">
       <c r="A224" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C224" s="1">
         <v>96.94999999999999</v>
@@ -3675,10 +4353,13 @@
       <c r="D224" s="1">
         <v>81.97999999999999</v>
       </c>
-    </row>
-    <row r="225" spans="1:4">
+      <c r="E224" s="1">
+        <v>165.84</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5">
       <c r="A225" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C225" s="1">
         <v>453.47</v>
@@ -3686,10 +4367,13 @@
       <c r="D225" s="1">
         <v>402.5700000000001</v>
       </c>
-    </row>
-    <row r="226" spans="1:4">
+      <c r="E225" s="1">
+        <v>205.6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5">
       <c r="A226" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="C226" s="1">
         <v>232.01</v>
@@ -3697,10 +4381,13 @@
       <c r="D226" s="1">
         <v>184.34</v>
       </c>
-    </row>
-    <row r="227" spans="1:4">
+      <c r="E226" s="1">
+        <v>162.34</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5">
       <c r="A227" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C227" s="1">
         <v>255.02</v>
@@ -3708,10 +4395,13 @@
       <c r="D227" s="1">
         <v>117</v>
       </c>
-    </row>
-    <row r="228" spans="1:4">
+      <c r="E227" s="1">
+        <v>280.49</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5">
       <c r="A228" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="C228" s="1">
         <v>295.91</v>
@@ -3719,10 +4409,13 @@
       <c r="D228" s="1">
         <v>291.52</v>
       </c>
-    </row>
-    <row r="229" spans="1:4">
+      <c r="E228" s="1">
+        <v>195.28</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5">
       <c r="A229" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C229" s="1">
         <v>530.55</v>
@@ -3730,10 +4423,13 @@
       <c r="D229" s="1">
         <v>257.78</v>
       </c>
-    </row>
-    <row r="230" spans="1:4">
+      <c r="E229" s="1">
+        <v>208.28</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5">
       <c r="A230" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C230" s="1">
         <v>16.49</v>
@@ -3741,21 +4437,27 @@
       <c r="D230" s="1">
         <v>79.33000000000001</v>
       </c>
-    </row>
-    <row r="231" spans="1:4">
+      <c r="E230" s="1">
+        <v>67.88</v>
+      </c>
+    </row>
+    <row r="231" spans="1:5">
       <c r="A231" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C231" s="1">
-        <v>281.87</v>
+        <v>281.8700000000001</v>
       </c>
       <c r="D231" s="1">
         <v>136.67</v>
       </c>
-    </row>
-    <row r="232" spans="1:4">
+      <c r="E231" s="1">
+        <v>208.9</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5">
       <c r="A232" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C232" s="1">
         <v>100.96</v>
@@ -3763,10 +4465,13 @@
       <c r="D232" s="1">
         <v>100.96</v>
       </c>
-    </row>
-    <row r="233" spans="1:4">
+      <c r="E232" s="1">
+        <v>160.94</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5">
       <c r="A233" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C233" s="1">
         <v>294.89</v>
@@ -3774,43 +4479,55 @@
       <c r="D233" s="1">
         <v>183.08</v>
       </c>
-    </row>
-    <row r="234" spans="1:4">
+      <c r="E233" s="1">
+        <v>167.13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5">
       <c r="A234" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C234" s="1">
-        <v>463.0600000000001</v>
+        <v>463.0599999999999</v>
       </c>
       <c r="D234" s="1">
         <v>212.71</v>
       </c>
-    </row>
-    <row r="235" spans="1:4">
+      <c r="E234" s="1">
+        <v>185.95</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5">
       <c r="A235" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C235" s="1">
-        <v>598.1400000000001</v>
+        <v>598.1399999999999</v>
       </c>
       <c r="D235" s="1">
         <v>686.9</v>
       </c>
-    </row>
-    <row r="236" spans="1:4">
+      <c r="E235" s="1">
+        <v>385.88</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5">
       <c r="A236" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C236" s="1">
         <v>254.34</v>
       </c>
       <c r="D236" s="1">
-        <v>656.1</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
+        <v>656.1000000000001</v>
+      </c>
+      <c r="E236" s="1">
+        <v>244.68</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5">
       <c r="A237" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C237" s="1">
         <v>104.57</v>
@@ -3818,10 +4535,13 @@
       <c r="D237" s="1">
         <v>229.02</v>
       </c>
-    </row>
-    <row r="238" spans="1:4">
+      <c r="E237" s="1">
+        <v>228.11</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5">
       <c r="A238" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="C238" s="1">
         <v>117.53</v>
@@ -3829,10 +4549,13 @@
       <c r="D238" s="1">
         <v>43.68</v>
       </c>
-    </row>
-    <row r="239" spans="1:4">
+      <c r="E238" s="1">
+        <v>206.32</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5">
       <c r="A239" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="C239" s="1">
         <v>190.93</v>
@@ -3840,10 +4563,13 @@
       <c r="D239" s="1">
         <v>114.55</v>
       </c>
-    </row>
-    <row r="240" spans="1:4">
+      <c r="E239" s="1">
+        <v>114.97</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5">
       <c r="A240" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C240" s="1">
         <v>148.16</v>
@@ -3851,10 +4577,13 @@
       <c r="D240" s="1">
         <v>144.87</v>
       </c>
-    </row>
-    <row r="241" spans="1:4">
+      <c r="E240" s="1">
+        <v>55.79</v>
+      </c>
+    </row>
+    <row r="241" spans="1:5">
       <c r="A241" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C241" s="1">
         <v>154.45</v>
@@ -3862,10 +4591,13 @@
       <c r="D241" s="1">
         <v>203.02</v>
       </c>
-    </row>
-    <row r="242" spans="1:4">
+      <c r="E241" s="1">
+        <v>140.27</v>
+      </c>
+    </row>
+    <row r="242" spans="1:5">
       <c r="A242" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C242" s="1">
         <v>154.95</v>
@@ -3873,10 +4605,13 @@
       <c r="D242" s="1">
         <v>127.95</v>
       </c>
-    </row>
-    <row r="243" spans="1:4">
+      <c r="E242" s="1">
+        <v>152.13</v>
+      </c>
+    </row>
+    <row r="243" spans="1:5">
       <c r="A243" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="C243" s="1">
         <v>471.21</v>
@@ -3884,21 +4619,27 @@
       <c r="D243" s="1">
         <v>101.95</v>
       </c>
-    </row>
-    <row r="244" spans="1:4">
+      <c r="E243" s="1">
+        <v>333.7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:5">
       <c r="A244" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="C244" s="1">
-        <v>377.88</v>
+        <v>377.8800000000001</v>
       </c>
       <c r="D244" s="1">
         <v>402.61</v>
       </c>
-    </row>
-    <row r="245" spans="1:4">
+      <c r="E244" s="1">
+        <v>341.52</v>
+      </c>
+    </row>
+    <row r="245" spans="1:5">
       <c r="A245" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C245" s="1">
         <v>250.74</v>
@@ -3906,10 +4647,13 @@
       <c r="D245" s="1">
         <v>283.54</v>
       </c>
-    </row>
-    <row r="246" spans="1:4">
+      <c r="E245" s="1">
+        <v>430.75</v>
+      </c>
+    </row>
+    <row r="246" spans="1:5">
       <c r="A246" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C246" s="1">
         <v>453.83</v>
@@ -3917,10 +4661,13 @@
       <c r="D246" s="1">
         <v>319.51</v>
       </c>
-    </row>
-    <row r="247" spans="1:4">
+      <c r="E246" s="1">
+        <v>279.38</v>
+      </c>
+    </row>
+    <row r="247" spans="1:5">
       <c r="A247" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C247" s="1">
         <v>245.04</v>
@@ -3928,10 +4675,13 @@
       <c r="D247" s="1">
         <v>245.84</v>
       </c>
-    </row>
-    <row r="248" spans="1:4">
+      <c r="E247" s="1">
+        <v>145.96</v>
+      </c>
+    </row>
+    <row r="248" spans="1:5">
       <c r="A248" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="C248" s="1">
         <v>155.97</v>
@@ -3939,10 +4689,13 @@
       <c r="D248" s="1">
         <v>138.27</v>
       </c>
-    </row>
-    <row r="249" spans="1:4">
+      <c r="E248" s="1">
+        <v>125.58</v>
+      </c>
+    </row>
+    <row r="249" spans="1:5">
       <c r="A249" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C249" s="1">
         <v>467.3</v>
@@ -3950,10 +4703,13 @@
       <c r="D249" s="1">
         <v>689.5599999999999</v>
       </c>
-    </row>
-    <row r="250" spans="1:4">
+      <c r="E249" s="1">
+        <v>647.73</v>
+      </c>
+    </row>
+    <row r="250" spans="1:5">
       <c r="A250" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="C250" s="1">
         <v>131.06</v>
@@ -3961,10 +4717,13 @@
       <c r="D250" s="1">
         <v>131.67</v>
       </c>
-    </row>
-    <row r="251" spans="1:4">
+      <c r="E250" s="1">
+        <v>191.14</v>
+      </c>
+    </row>
+    <row r="251" spans="1:5">
       <c r="A251" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C251" s="1">
         <v>716.7</v>
@@ -3972,10 +4731,13 @@
       <c r="D251" s="1">
         <v>1082.25</v>
       </c>
-    </row>
-    <row r="252" spans="1:4">
+      <c r="E251" s="1">
+        <v>752.9400000000001</v>
+      </c>
+    </row>
+    <row r="252" spans="1:5">
       <c r="A252" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C252" s="1">
         <v>125.71</v>
@@ -3983,10 +4745,13 @@
       <c r="D252" s="1">
         <v>37.99</v>
       </c>
-    </row>
-    <row r="253" spans="1:4">
+      <c r="E252" s="1">
+        <v>54.48</v>
+      </c>
+    </row>
+    <row r="253" spans="1:5">
       <c r="A253" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C253" s="1">
         <v>118.06</v>
@@ -3994,10 +4759,13 @@
       <c r="D253" s="1">
         <v>92.95999999999999</v>
       </c>
-    </row>
-    <row r="254" spans="1:4">
+      <c r="E253" s="1">
+        <v>167.31</v>
+      </c>
+    </row>
+    <row r="254" spans="1:5">
       <c r="A254" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C254" s="1">
         <v>116.53</v>
@@ -4005,10 +4773,13 @@
       <c r="D254" s="1">
         <v>103.07</v>
       </c>
-    </row>
-    <row r="255" spans="1:4">
+      <c r="E254" s="1">
+        <v>80.27</v>
+      </c>
+    </row>
+    <row r="255" spans="1:5">
       <c r="A255" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C255" s="1">
         <v>241.71</v>
@@ -4016,10 +4787,13 @@
       <c r="D255" s="1">
         <v>52.48</v>
       </c>
-    </row>
-    <row r="256" spans="1:4">
+      <c r="E255" s="1">
+        <v>197.89</v>
+      </c>
+    </row>
+    <row r="256" spans="1:5">
       <c r="A256" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C256" s="1">
         <v>369.1700000000001</v>
@@ -4027,10 +4801,13 @@
       <c r="D256" s="1">
         <v>212.76</v>
       </c>
-    </row>
-    <row r="257" spans="1:4">
+      <c r="E256" s="1">
+        <v>453.48</v>
+      </c>
+    </row>
+    <row r="257" spans="1:5">
       <c r="A257" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="C257" s="1">
         <v>82.98999999999999</v>
@@ -4038,10 +4815,13 @@
       <c r="D257" s="1">
         <v>176.33</v>
       </c>
-    </row>
-    <row r="258" spans="1:4">
+      <c r="E257" s="1">
+        <v>53.67</v>
+      </c>
+    </row>
+    <row r="258" spans="1:5">
       <c r="A258" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C258" s="1">
         <v>111.37</v>
@@ -4049,10 +4829,13 @@
       <c r="D258" s="1">
         <v>139.51</v>
       </c>
-    </row>
-    <row r="259" spans="1:4">
+      <c r="E258" s="1">
+        <v>194.19</v>
+      </c>
+    </row>
+    <row r="259" spans="1:5">
       <c r="A259" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C259" s="1">
         <v>101.97</v>
@@ -4060,21 +4843,27 @@
       <c r="D259" s="1">
         <v>170.69</v>
       </c>
-    </row>
-    <row r="260" spans="1:4">
+      <c r="E259" s="1">
+        <v>39.58</v>
+      </c>
+    </row>
+    <row r="260" spans="1:5">
       <c r="A260" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="C260" s="1">
         <v>223.84</v>
       </c>
       <c r="D260" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
+        <v>43</v>
+      </c>
+      <c r="E260" s="1">
+        <v>559.9200000000001</v>
+      </c>
+    </row>
+    <row r="261" spans="1:5">
       <c r="A261" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C261" s="1">
         <v>338.76</v>
@@ -4082,10 +4871,13 @@
       <c r="D261" s="1">
         <v>196.58</v>
       </c>
-    </row>
-    <row r="262" spans="1:4">
+      <c r="E261" s="1">
+        <v>173.92</v>
+      </c>
+    </row>
+    <row r="262" spans="1:5">
       <c r="A262" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="C262" s="1">
         <v>334.64</v>
@@ -4093,21 +4885,27 @@
       <c r="D262" s="1">
         <v>188.74</v>
       </c>
-    </row>
-    <row r="263" spans="1:4">
+      <c r="E262" s="1">
+        <v>319.6500000000001</v>
+      </c>
+    </row>
+    <row r="263" spans="1:5">
       <c r="A263" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="C263" s="1">
         <v>435.01</v>
       </c>
       <c r="D263" s="1">
-        <v>404.4299999999999</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
+        <v>404.4300000000001</v>
+      </c>
+      <c r="E263" s="1">
+        <v>902.6600000000001</v>
+      </c>
+    </row>
+    <row r="264" spans="1:5">
       <c r="A264" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C264" s="1">
         <v>150.09</v>
@@ -4115,10 +4913,13 @@
       <c r="D264" s="1">
         <v>220.08</v>
       </c>
-    </row>
-    <row r="265" spans="1:4">
+      <c r="E264" s="1">
+        <v>116.61</v>
+      </c>
+    </row>
+    <row r="265" spans="1:5">
       <c r="A265" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C265" s="1">
         <v>181.58</v>
@@ -4126,21 +4927,27 @@
       <c r="D265" s="1">
         <v>208.57</v>
       </c>
-    </row>
-    <row r="266" spans="1:4">
+      <c r="E265" s="1">
+        <v>144.55</v>
+      </c>
+    </row>
+    <row r="266" spans="1:5">
       <c r="A266" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="C266" s="1">
-        <v>675.6400000000001</v>
+        <v>675.64</v>
       </c>
       <c r="D266" s="1">
-        <v>885.2100000000002</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
+        <v>885.2099999999999</v>
+      </c>
+      <c r="E266" s="1">
+        <v>919.0300000000001</v>
+      </c>
+    </row>
+    <row r="267" spans="1:5">
       <c r="A267" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C267" s="1">
         <v>620.5</v>
@@ -4148,10 +4955,13 @@
       <c r="D267" s="1">
         <v>616.96</v>
       </c>
-    </row>
-    <row r="268" spans="1:4">
+      <c r="E267" s="1">
+        <v>414.58</v>
+      </c>
+    </row>
+    <row r="268" spans="1:5">
       <c r="A268" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="C268" s="1">
         <v>252.87</v>
@@ -4159,21 +4969,27 @@
       <c r="D268" s="1">
         <v>199.78</v>
       </c>
-    </row>
-    <row r="269" spans="1:4">
+      <c r="E268" s="1">
+        <v>101.21</v>
+      </c>
+    </row>
+    <row r="269" spans="1:5">
       <c r="A269" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C269" s="1">
         <v>56.56999999999999</v>
       </c>
       <c r="D269" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
+        <v>43</v>
+      </c>
+      <c r="E269" s="1">
+        <v>69.88</v>
+      </c>
+    </row>
+    <row r="270" spans="1:5">
       <c r="A270" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C270" s="1">
         <v>127.57</v>
@@ -4181,9 +4997,40 @@
       <c r="D270" s="1">
         <v>111.94</v>
       </c>
+      <c r="E270" s="1">
+        <v>157.78</v>
+      </c>
+    </row>
+    <row r="271" spans="1:5">
+      <c r="A271" t="s">
+        <v>275</v>
+      </c>
+      <c r="C271" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D271" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E271" s="1">
+        <v>16.99</v>
+      </c>
+    </row>
+    <row r="272" spans="1:5">
+      <c r="A272" t="s">
+        <v>276</v>
+      </c>
+      <c r="C272" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D272" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E272" s="1">
+        <v>86.23</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="269">
+  <mergeCells count="271">
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -4453,6 +5300,8 @@
     <mergeCell ref="A268:B268"/>
     <mergeCell ref="A269:B269"/>
     <mergeCell ref="A270:B270"/>
+    <mergeCell ref="A271:B271"/>
+    <mergeCell ref="A272:B272"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
